--- a/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,13 +145,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -175,10 +175,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -203,10 +203,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -231,10 +231,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -259,10 +259,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -287,10 +287,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -315,10 +315,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -343,10 +343,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -394,8 +394,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -411,7 +411,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -424,7 +424,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -448,9 +448,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2053,25 +2053,25 @@
         <v>46266</v>
       </c>
       <c r="B46" t="n">
-        <v>32489.67433267251</v>
+        <v>32325.5553828973</v>
       </c>
       <c r="C46" t="n">
-        <v>22073.33657885778</v>
+        <v>22244.82389970851</v>
       </c>
       <c r="D46" t="n">
-        <v>8356.356061516279</v>
+        <v>8246.464022482769</v>
       </c>
       <c r="E46" t="n">
-        <v>11455.89385137571</v>
+        <v>11429.70140426172</v>
       </c>
       <c r="F46" t="n">
-        <v>5586.949693620089</v>
+        <v>5532.419010402095</v>
       </c>
       <c r="G46" t="n">
         <v>992.1941964285714</v>
       </c>
       <c r="H46" t="n">
-        <v>130.0044575273339</v>
+        <v>135.3294914248413</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1367"/>
+  <dimension ref="A1:M1368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -54067,6 +54067,44 @@
         <v>287</v>
       </c>
     </row>
+    <row r="1368">
+      <c r="A1368" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1368" t="n">
+        <v>10670.1204379562</v>
+      </c>
+      <c r="C1368" t="n">
+        <v>27217.95620437956</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>27566.10583941606</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>5059.594890510949</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>3951.029197080292</v>
+      </c>
+      <c r="H1368" t="n">
+        <v>14.75547445255475</v>
+      </c>
+      <c r="I1368" t="n">
+        <v>1252.284671532847</v>
+      </c>
+      <c r="J1368" t="n">
+        <v>81382.45398805574</v>
+      </c>
+      <c r="K1368" t="n">
+        <v>5650.607272727273</v>
+      </c>
+      <c r="L1368" t="n">
+        <v>0.1107194935276061</v>
+      </c>
+      <c r="M1368" t="n">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
@@ -2053,25 +2053,25 @@
         <v>46266</v>
       </c>
       <c r="B46" t="n">
-        <v>32325.5553828973</v>
+        <v>32322.45768242259</v>
       </c>
       <c r="C46" t="n">
-        <v>22244.82389970851</v>
+        <v>22246.35135023851</v>
       </c>
       <c r="D46" t="n">
-        <v>8246.464022482769</v>
+        <v>8251.622747577625</v>
       </c>
       <c r="E46" t="n">
-        <v>11429.70140426172</v>
+        <v>11429.67221483801</v>
       </c>
       <c r="F46" t="n">
-        <v>5532.419010402095</v>
+        <v>5526.893095441144</v>
       </c>
       <c r="G46" t="n">
         <v>992.1941964285714</v>
       </c>
       <c r="H46" t="n">
-        <v>135.3294914248413</v>
+        <v>135.5769196657001</v>
       </c>
     </row>
   </sheetData>
@@ -54072,37 +54072,37 @@
         <v>46295</v>
       </c>
       <c r="B1368" t="n">
-        <v>10670.1204379562</v>
+        <v>10669.24475524476</v>
       </c>
       <c r="C1368" t="n">
-        <v>27217.95620437956</v>
+        <v>27263.77972027972</v>
       </c>
       <c r="D1368" t="n">
-        <v>27566.10583941606</v>
+        <v>27473.17482517482</v>
       </c>
       <c r="F1368" t="n">
-        <v>5059.594890510949</v>
+        <v>5214.356643356643</v>
       </c>
       <c r="G1368" t="n">
-        <v>3951.029197080292</v>
+        <v>3785.251748251748</v>
       </c>
       <c r="H1368" t="n">
-        <v>14.75547445255475</v>
+        <v>10.17832167832168</v>
       </c>
       <c r="I1368" t="n">
-        <v>1252.284671532847</v>
+        <v>1202.93006993007</v>
       </c>
       <c r="J1368" t="n">
-        <v>81382.45398805574</v>
+        <v>81162.0380351356</v>
       </c>
       <c r="K1368" t="n">
-        <v>5650.607272727273</v>
+        <v>5543.121951219512</v>
       </c>
       <c r="L1368" t="n">
-        <v>0.1107194935276061</v>
+        <v>0.1108844554607217</v>
       </c>
       <c r="M1368" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>MISO fuel mix (monthly average) (to Sep/26)</a:t>
+              <a:t>MISO fuel mix (monthly average) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$46</f>
+              <f>'Chart'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$46</f>
+              <f>'Chart'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$46</f>
+              <f>'Chart'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$46</f>
+              <f>'Chart'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$46</f>
+              <f>'Chart'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$46</f>
+              <f>'Chart'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$46</f>
+              <f>'Chart'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$46</f>
+              <f>'Chart'!$E$2:$E$47</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$46</f>
+              <f>'Chart'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$46</f>
+              <f>'Chart'!$F$2:$F$47</f>
             </numRef>
           </val>
         </ser>
@@ -326,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$46</f>
+              <f>'Chart'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$46</f>
+              <f>'Chart'!$G$2:$G$47</f>
             </numRef>
           </val>
         </ser>
@@ -354,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$46</f>
+              <f>'Chart'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$46</f>
+              <f>'Chart'!$H$2:$H$47</f>
             </numRef>
           </val>
         </ser>
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2087,6 +2087,32 @@
       </c>
       <c r="H46" t="n">
         <v>128.1701388888889</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B47" t="n">
+        <v>32036.8</v>
+      </c>
+      <c r="C47" t="n">
+        <v>19626.6125</v>
+      </c>
+      <c r="D47" t="n">
+        <v>12634.1125</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10511.4125</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3840.270833333333</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1070.929166666667</v>
+      </c>
+      <c r="H47" t="n">
+        <v>119.7666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2101,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1368"/>
+  <dimension ref="A1:L1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -54115,6 +54141,44 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1369">
+      <c r="A1369" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1369" t="n">
+        <v>10511.4125</v>
+      </c>
+      <c r="C1369" t="n">
+        <v>19626.6125</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>32036.8</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>1070.929166666667</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>12634.1125</v>
+      </c>
+      <c r="G1369" t="n">
+        <v>3840.270833333333</v>
+      </c>
+      <c r="H1369" t="n">
+        <v>95.76666666666665</v>
+      </c>
+      <c r="I1369" t="n">
+        <v>802.225</v>
+      </c>
+      <c r="J1369" t="n">
+        <v>80618.12916666667</v>
+      </c>
+      <c r="K1369" t="n">
+        <v>0.2043508513981372</v>
+      </c>
+      <c r="L1369" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>MISO fuel mix (monthly average) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -205,7 +206,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -261,7 +262,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -289,7 +290,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -317,7 +318,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -950,7 +951,7 @@
         <v>44958</v>
       </c>
       <c r="B3" t="n">
-        <v>24381.37559523809</v>
+        <v>24381.3755952381</v>
       </c>
       <c r="C3" t="n">
         <v>17045.79880952381</v>
@@ -962,7 +963,7 @@
         <v>10941.25044642857</v>
       </c>
       <c r="F3" t="n">
-        <v>474.3438988095239</v>
+        <v>474.3438988095238</v>
       </c>
       <c r="G3" t="n">
         <v>1334.862797619048</v>
@@ -1014,7 +1015,7 @@
         <v>9614.496666666668</v>
       </c>
       <c r="F5" t="n">
-        <v>706.9069444444444</v>
+        <v>706.9069444444445</v>
       </c>
       <c r="G5" t="n">
         <v>1386.888611111111</v>
@@ -1040,7 +1041,7 @@
         <v>8810.655510752689</v>
       </c>
       <c r="F6" t="n">
-        <v>952.9313172043011</v>
+        <v>952.931317204301</v>
       </c>
       <c r="G6" t="n">
         <v>1429.286290322581</v>
@@ -1083,7 +1084,7 @@
         <v>35518.61962365591</v>
       </c>
       <c r="C8" t="n">
-        <v>26055.46075268817</v>
+        <v>26055.46075268818</v>
       </c>
       <c r="D8" t="n">
         <v>5165.126747311828</v>
@@ -1112,7 +1113,7 @@
         <v>25860.24569892473</v>
       </c>
       <c r="D9" t="n">
-        <v>7081.211290322582</v>
+        <v>7081.211290322581</v>
       </c>
       <c r="E9" t="n">
         <v>11182.7498655914</v>
@@ -1132,7 +1133,7 @@
         <v>45170</v>
       </c>
       <c r="B10" t="n">
-        <v>28318.75666666666</v>
+        <v>28318.75666666667</v>
       </c>
       <c r="C10" t="n">
         <v>22155.84638888889</v>
@@ -1164,16 +1165,16 @@
         <v>19616.14018817204</v>
       </c>
       <c r="D11" t="n">
-        <v>11646.3372311828</v>
+        <v>11646.33723118279</v>
       </c>
       <c r="E11" t="n">
         <v>7828.598252688173</v>
       </c>
       <c r="F11" t="n">
-        <v>693.9899193548387</v>
+        <v>693.9899193548388</v>
       </c>
       <c r="G11" t="n">
-        <v>678.0114247311828</v>
+        <v>678.0114247311826</v>
       </c>
       <c r="H11" t="n">
         <v>25.36370967741935</v>
@@ -1216,7 +1217,7 @@
         <v>19540.26021505376</v>
       </c>
       <c r="D13" t="n">
-        <v>11768.67768817204</v>
+        <v>11768.67768817205</v>
       </c>
       <c r="E13" t="n">
         <v>8667.809139784946</v>
@@ -1236,7 +1237,7 @@
         <v>45292</v>
       </c>
       <c r="B14" t="n">
-        <v>29720.9186827957</v>
+        <v>29720.91868279571</v>
       </c>
       <c r="C14" t="n">
         <v>26741.10241935484</v>
@@ -1245,10 +1246,10 @@
         <v>10658.91693548387</v>
       </c>
       <c r="E14" t="n">
-        <v>9193.04126344086</v>
+        <v>9193.041263440859</v>
       </c>
       <c r="F14" t="n">
-        <v>450.7774193548387</v>
+        <v>450.7774193548386</v>
       </c>
       <c r="G14" t="n">
         <v>1048.117069892473</v>
@@ -1314,7 +1315,7 @@
         <v>45383</v>
       </c>
       <c r="B17" t="n">
-        <v>23760.28069444444</v>
+        <v>23760.28069444445</v>
       </c>
       <c r="C17" t="n">
         <v>12971.39361111111</v>
@@ -1323,7 +1324,7 @@
         <v>15502.02888888889</v>
       </c>
       <c r="E17" t="n">
-        <v>9411.021805555556</v>
+        <v>9411.021805555558</v>
       </c>
       <c r="F17" t="n">
         <v>1529.826944444445</v>
@@ -1349,7 +1350,7 @@
         <v>10513.97540322581</v>
       </c>
       <c r="E18" t="n">
-        <v>9605.854838709678</v>
+        <v>9605.854838709676</v>
       </c>
       <c r="F18" t="n">
         <v>1964.007258064516</v>
@@ -1366,7 +1367,7 @@
         <v>45444</v>
       </c>
       <c r="B19" t="n">
-        <v>30313.10444444445</v>
+        <v>30313.10444444443</v>
       </c>
       <c r="C19" t="n">
         <v>21769.18416666667</v>
@@ -1378,10 +1379,10 @@
         <v>11095.71055555556</v>
       </c>
       <c r="F19" t="n">
-        <v>2103.602083333333</v>
+        <v>2103.602083333334</v>
       </c>
       <c r="G19" t="n">
-        <v>1884.810972222222</v>
+        <v>1884.810972222223</v>
       </c>
       <c r="H19" t="n">
         <v>26.16625</v>
@@ -1392,7 +1393,7 @@
         <v>45474</v>
       </c>
       <c r="B20" t="n">
-        <v>37576.17836021505</v>
+        <v>37576.17836021506</v>
       </c>
       <c r="C20" t="n">
         <v>23434.98319892473</v>
@@ -1424,13 +1425,13 @@
         <v>22816.27728494624</v>
       </c>
       <c r="D21" t="n">
-        <v>7005.63440860215</v>
+        <v>7005.634408602151</v>
       </c>
       <c r="E21" t="n">
         <v>11471.90309139785</v>
       </c>
       <c r="F21" t="n">
-        <v>2355.899462365591</v>
+        <v>2355.899462365592</v>
       </c>
       <c r="G21" t="n">
         <v>1411.068010752688</v>
@@ -1456,7 +1457,7 @@
         <v>11216.85986111111</v>
       </c>
       <c r="F22" t="n">
-        <v>2088.284166666666</v>
+        <v>2088.284166666667</v>
       </c>
       <c r="G22" t="n">
         <v>1009.431388888889</v>
@@ -1473,7 +1474,7 @@
         <v>24609.83400537634</v>
       </c>
       <c r="C23" t="n">
-        <v>16517.60793010753</v>
+        <v>16517.60793010752</v>
       </c>
       <c r="D23" t="n">
         <v>13264.64798387097</v>
@@ -1548,7 +1549,7 @@
         <v>45658</v>
       </c>
       <c r="B26" t="n">
-        <v>26140.49072580645</v>
+        <v>26140.49072580646</v>
       </c>
       <c r="C26" t="n">
         <v>26830.0375</v>
@@ -1606,13 +1607,13 @@
         <v>17425.28158602151</v>
       </c>
       <c r="D28" t="n">
-        <v>15259.28588709677</v>
+        <v>15259.28588709678</v>
       </c>
       <c r="E28" t="n">
         <v>10337.93629032258</v>
       </c>
       <c r="F28" t="n">
-        <v>3141.303897849462</v>
+        <v>3141.303897849463</v>
       </c>
       <c r="G28" t="n">
         <v>1260.3625</v>
@@ -1632,10 +1633,10 @@
         <v>16536.16083333334</v>
       </c>
       <c r="D29" t="n">
-        <v>14052.28041666667</v>
+        <v>14052.28041666666</v>
       </c>
       <c r="E29" t="n">
-        <v>9565.762500000001</v>
+        <v>9565.762499999999</v>
       </c>
       <c r="F29" t="n">
         <v>3436.176388888889</v>
@@ -1644,7 +1645,7 @@
         <v>1368.80125</v>
       </c>
       <c r="H29" t="n">
-        <v>43.75708333333333</v>
+        <v>43.75708333333334</v>
       </c>
     </row>
     <row r="30">
@@ -1664,13 +1665,13 @@
         <v>8676.183064516128</v>
       </c>
       <c r="F30" t="n">
-        <v>3926.670833333334</v>
+        <v>3926.670833333333</v>
       </c>
       <c r="G30" t="n">
-        <v>1456.934274193548</v>
+        <v>1456.934274193549</v>
       </c>
       <c r="H30" t="n">
-        <v>48.91572580645162</v>
+        <v>48.91572580645161</v>
       </c>
     </row>
     <row r="31">
@@ -1687,13 +1688,13 @@
         <v>8794.564305555554</v>
       </c>
       <c r="E31" t="n">
-        <v>9759.228888888889</v>
+        <v>9759.228888888891</v>
       </c>
       <c r="F31" t="n">
         <v>4432.657638888889</v>
       </c>
       <c r="G31" t="n">
-        <v>1459.880694444444</v>
+        <v>1459.880694444445</v>
       </c>
       <c r="H31" t="n">
         <v>65.58930555555555</v>
@@ -1710,7 +1711,7 @@
         <v>26833.41545698925</v>
       </c>
       <c r="D32" t="n">
-        <v>6175.878360215053</v>
+        <v>6175.878360215052</v>
       </c>
       <c r="E32" t="n">
         <v>11085.93387096774</v>
@@ -1730,16 +1731,16 @@
         <v>45870</v>
       </c>
       <c r="B33" t="n">
-        <v>33902.74798387097</v>
+        <v>33902.74798387098</v>
       </c>
       <c r="C33" t="n">
-        <v>23792.19516129032</v>
+        <v>23792.19516129033</v>
       </c>
       <c r="D33" t="n">
         <v>5921.219758064516</v>
       </c>
       <c r="E33" t="n">
-        <v>11377.13588709677</v>
+        <v>11377.13588709678</v>
       </c>
       <c r="F33" t="n">
         <v>4903.48064516129</v>
@@ -1762,19 +1763,19 @@
         <v>21183.40166666667</v>
       </c>
       <c r="D34" t="n">
-        <v>6683.318472222222</v>
+        <v>6683.318472222223</v>
       </c>
       <c r="E34" t="n">
         <v>10604.00597222222</v>
       </c>
       <c r="F34" t="n">
-        <v>4334.123333333333</v>
+        <v>4334.123333333334</v>
       </c>
       <c r="G34" t="n">
         <v>954.4834722222222</v>
       </c>
       <c r="H34" t="n">
-        <v>78.40375</v>
+        <v>78.40374999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1797,7 +1798,7 @@
         <v>3468.046774193548</v>
       </c>
       <c r="G35" t="n">
-        <v>681.6672043010753</v>
+        <v>681.6672043010752</v>
       </c>
       <c r="H35" t="n">
         <v>78.84677419354838</v>
@@ -1808,7 +1809,7 @@
         <v>45962</v>
       </c>
       <c r="B36" t="n">
-        <v>24710.72736111111</v>
+        <v>24710.7273611111</v>
       </c>
       <c r="C36" t="n">
         <v>20005.79569444444</v>
@@ -1826,7 +1827,7 @@
         <v>705.8545833333334</v>
       </c>
       <c r="H36" t="n">
-        <v>86.68166666666667</v>
+        <v>86.68166666666666</v>
       </c>
     </row>
     <row r="37">
@@ -1834,7 +1835,7 @@
         <v>45992</v>
       </c>
       <c r="B37" t="n">
-        <v>26363.89892473118</v>
+        <v>26363.89892473119</v>
       </c>
       <c r="C37" t="n">
         <v>24442.39086021505</v>
@@ -1843,16 +1844,16 @@
         <v>14197.81397849462</v>
       </c>
       <c r="E37" t="n">
-        <v>11896.37849462366</v>
+        <v>11896.37849462365</v>
       </c>
       <c r="F37" t="n">
         <v>1792.197446236559</v>
       </c>
       <c r="G37" t="n">
-        <v>808.2056451612904</v>
+        <v>808.2056451612905</v>
       </c>
       <c r="H37" t="n">
-        <v>77.98561827956989</v>
+        <v>77.98561827956991</v>
       </c>
     </row>
     <row r="38">
@@ -1866,16 +1867,16 @@
         <v>24066.92819444444</v>
       </c>
       <c r="D38" t="n">
-        <v>14041.11680555556</v>
+        <v>14041.11680555555</v>
       </c>
       <c r="E38" t="n">
         <v>11894.78291666667</v>
       </c>
       <c r="F38" t="n">
-        <v>2653.537222222222</v>
+        <v>2653.537222222223</v>
       </c>
       <c r="G38" t="n">
-        <v>880.7813888888888</v>
+        <v>880.7813888888891</v>
       </c>
       <c r="H38" t="n">
         <v>96.40916666666666</v>
@@ -1898,7 +1899,7 @@
         <v>10723.33244047619</v>
       </c>
       <c r="F39" t="n">
-        <v>3668.634672619047</v>
+        <v>3668.634672619048</v>
       </c>
       <c r="G39" t="n">
         <v>846.2117559523809</v>
@@ -1912,7 +1913,7 @@
         <v>46082</v>
       </c>
       <c r="B40" t="n">
-        <v>25130.88158602151</v>
+        <v>25130.8815860215</v>
       </c>
       <c r="C40" t="n">
         <v>16165.23427419355</v>
@@ -1970,16 +1971,16 @@
         <v>14681.80940860215</v>
       </c>
       <c r="D42" t="n">
-        <v>11692.83212365591</v>
+        <v>11692.83212365592</v>
       </c>
       <c r="E42" t="n">
         <v>10879.11034946237</v>
       </c>
       <c r="F42" t="n">
-        <v>6098.584408602151</v>
+        <v>6098.584408602152</v>
       </c>
       <c r="G42" t="n">
-        <v>1450.338575268817</v>
+        <v>1450.338575268818</v>
       </c>
       <c r="H42" t="n">
         <v>119.9922043010753</v>
@@ -1993,7 +1994,7 @@
         <v>30130.77226386806</v>
       </c>
       <c r="C43" t="n">
-        <v>18668.80142428786</v>
+        <v>18668.80142428785</v>
       </c>
       <c r="D43" t="n">
         <v>10115.39731384308</v>
@@ -2002,7 +2003,7 @@
         <v>11409.77762368816</v>
       </c>
       <c r="F43" t="n">
-        <v>6659.618828085958</v>
+        <v>6659.618828085957</v>
       </c>
       <c r="G43" t="n">
         <v>1370.445064967516</v>
@@ -2016,7 +2017,7 @@
         <v>46204</v>
       </c>
       <c r="B44" t="n">
-        <v>37955.85672043011</v>
+        <v>37955.8567204301</v>
       </c>
       <c r="C44" t="n">
         <v>25478.52083333334</v>
@@ -2048,16 +2049,16 @@
         <v>24390.52768817205</v>
       </c>
       <c r="D45" t="n">
-        <v>6565.659274193548</v>
+        <v>6565.659274193549</v>
       </c>
       <c r="E45" t="n">
         <v>10818.93602150538</v>
       </c>
       <c r="F45" t="n">
-        <v>6587.08306451613</v>
+        <v>6587.083064516129</v>
       </c>
       <c r="G45" t="n">
-        <v>965.6180107526882</v>
+        <v>965.6180107526883</v>
       </c>
       <c r="H45" t="n">
         <v>112.7106182795699</v>
@@ -2074,7 +2075,7 @@
         <v>21888.69805555556</v>
       </c>
       <c r="D46" t="n">
-        <v>8251.488055555556</v>
+        <v>8251.488055555557</v>
       </c>
       <c r="E46" t="n">
         <v>11423.04958333333</v>
@@ -2094,25 +2095,25 @@
         <v>46296</v>
       </c>
       <c r="B47" t="n">
-        <v>32036.8</v>
+        <v>26548.88429487179</v>
       </c>
       <c r="C47" t="n">
-        <v>19626.6125</v>
+        <v>17474.57243589743</v>
       </c>
       <c r="D47" t="n">
-        <v>12634.1125</v>
+        <v>11300.04711538461</v>
       </c>
       <c r="E47" t="n">
-        <v>10511.4125</v>
+        <v>9198.352083333333</v>
       </c>
       <c r="F47" t="n">
-        <v>3840.270833333333</v>
+        <v>5482.638942307693</v>
       </c>
       <c r="G47" t="n">
-        <v>1070.929166666667</v>
+        <v>804.1891025641027</v>
       </c>
       <c r="H47" t="n">
-        <v>119.7666666666667</v>
+        <v>130.3455128205128</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1369"/>
+  <dimension ref="A1:L1394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -54179,6 +54180,956 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1370">
+      <c r="A1370" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1370" t="n">
+        <v>10154.10833333333</v>
+      </c>
+      <c r="C1370" t="n">
+        <v>18743.50416666667</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>30968.47083333333</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>962.8375</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>7848.391666666667</v>
+      </c>
+      <c r="G1370" t="n">
+        <v>4198.974999999999</v>
+      </c>
+      <c r="H1370" t="n">
+        <v>69.8625</v>
+      </c>
+      <c r="I1370" t="n">
+        <v>567.0666666666667</v>
+      </c>
+      <c r="J1370" t="n">
+        <v>73513.21666666666</v>
+      </c>
+      <c r="K1370" t="n">
+        <v>0.1638802818450107</v>
+      </c>
+      <c r="L1370" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1371" t="n">
+        <v>9973.429166666667</v>
+      </c>
+      <c r="C1371" t="n">
+        <v>17172.3375</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>24120.99166666667</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>885.875</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>12271.04166666667</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>5713.879166666666</v>
+      </c>
+      <c r="H1371" t="n">
+        <v>85.56666666666668</v>
+      </c>
+      <c r="I1371" t="n">
+        <v>520.3041666666667</v>
+      </c>
+      <c r="J1371" t="n">
+        <v>70743.425</v>
+      </c>
+      <c r="K1371" t="n">
+        <v>0.2542274541179386</v>
+      </c>
+      <c r="L1371" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1372" t="n">
+        <v>9966.424999999999</v>
+      </c>
+      <c r="C1372" t="n">
+        <v>19156.875</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>24387.91666666667</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>903.7458333333334</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>7404.495833333333</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>6123.591666666667</v>
+      </c>
+      <c r="H1372" t="n">
+        <v>121.875</v>
+      </c>
+      <c r="I1372" t="n">
+        <v>521.4499999999999</v>
+      </c>
+      <c r="J1372" t="n">
+        <v>68586.375</v>
+      </c>
+      <c r="K1372" t="n">
+        <v>0.1972416168663237</v>
+      </c>
+      <c r="L1372" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1373" t="n">
+        <v>9981.091666666667</v>
+      </c>
+      <c r="C1373" t="n">
+        <v>18261.525</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>27866.83333333333</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>951.2333333333332</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>8205.983333333334</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>7121.008333333334</v>
+      </c>
+      <c r="H1373" t="n">
+        <v>109.0041666666667</v>
+      </c>
+      <c r="I1373" t="n">
+        <v>502.8666666666666</v>
+      </c>
+      <c r="J1373" t="n">
+        <v>72999.54583333334</v>
+      </c>
+      <c r="K1373" t="n">
+        <v>0.2099600962129274</v>
+      </c>
+      <c r="L1373" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1374" t="n">
+        <v>9986.970833333333</v>
+      </c>
+      <c r="C1374" t="n">
+        <v>16613.79166666667</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>25596.21666666667</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>963.6083333333332</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>13645.25</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>7010.379166666667</v>
+      </c>
+      <c r="H1374" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="I1374" t="n">
+        <v>507.2041666666667</v>
+      </c>
+      <c r="J1374" t="n">
+        <v>74407.07083333335</v>
+      </c>
+      <c r="K1374" t="n">
+        <v>0.2776030414224185</v>
+      </c>
+      <c r="L1374" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1375" t="n">
+        <v>9965.391666666668</v>
+      </c>
+      <c r="C1375" t="n">
+        <v>18300.975</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>27302.57916666667</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>971.775</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>9935.566666666666</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>6986.149999999999</v>
+      </c>
+      <c r="H1375" t="n">
+        <v>139.9125</v>
+      </c>
+      <c r="I1375" t="n">
+        <v>522.4833333333333</v>
+      </c>
+      <c r="J1375" t="n">
+        <v>74124.83333333333</v>
+      </c>
+      <c r="K1375" t="n">
+        <v>0.22828674151038</v>
+      </c>
+      <c r="L1375" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1376" t="n">
+        <v>9984.866666666667</v>
+      </c>
+      <c r="C1376" t="n">
+        <v>21637.21666666667</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>29665.50833333333</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>992.0875</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>4613.25</v>
+      </c>
+      <c r="G1376" t="n">
+        <v>6711.683333333333</v>
+      </c>
+      <c r="H1376" t="n">
+        <v>118.6041666666667</v>
+      </c>
+      <c r="I1376" t="n">
+        <v>550.6833333333334</v>
+      </c>
+      <c r="J1376" t="n">
+        <v>74273.89999999999</v>
+      </c>
+      <c r="K1376" t="n">
+        <v>0.1524752750741961</v>
+      </c>
+      <c r="L1376" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1377" t="n">
+        <v>9948.5</v>
+      </c>
+      <c r="C1377" t="n">
+        <v>17606.6</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>26486.97083333334</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>897.4958333333334</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>13776.62916666667</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>5886.866666666666</v>
+      </c>
+      <c r="H1377" t="n">
+        <v>103.1083333333333</v>
+      </c>
+      <c r="I1377" t="n">
+        <v>554.6999999999999</v>
+      </c>
+      <c r="J1377" t="n">
+        <v>75260.87083333333</v>
+      </c>
+      <c r="K1377" t="n">
+        <v>0.2612711707372949</v>
+      </c>
+      <c r="L1377" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1378" t="n">
+        <v>9334.379166666668</v>
+      </c>
+      <c r="C1378" t="n">
+        <v>15433.49583333333</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>20895.4125</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>766.8000000000002</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>19657.3</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>4261.554166666666</v>
+      </c>
+      <c r="H1378" t="n">
+        <v>78.9375</v>
+      </c>
+      <c r="I1378" t="n">
+        <v>568.7166666666667</v>
+      </c>
+      <c r="J1378" t="n">
+        <v>70996.59583333334</v>
+      </c>
+      <c r="K1378" t="n">
+        <v>0.3369014230318437</v>
+      </c>
+      <c r="L1378" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1379" t="n">
+        <v>9427.1875</v>
+      </c>
+      <c r="C1379" t="n">
+        <v>16714.8875</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>22716.39583333333</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>824.3208333333333</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>15056.07083333334</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>5900.912500000001</v>
+      </c>
+      <c r="H1379" t="n">
+        <v>111.2041666666667</v>
+      </c>
+      <c r="I1379" t="n">
+        <v>559.4125</v>
+      </c>
+      <c r="J1379" t="n">
+        <v>71310.39166666666</v>
+      </c>
+      <c r="K1379" t="n">
+        <v>0.2938840026471131</v>
+      </c>
+      <c r="L1379" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1380" t="n">
+        <v>9344.791666666666</v>
+      </c>
+      <c r="C1380" t="n">
+        <v>18288.8125</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>26708.4375</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>934.9291666666667</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>16125.67083333334</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>6090.5</v>
+      </c>
+      <c r="H1380" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="I1380" t="n">
+        <v>819.1166666666667</v>
+      </c>
+      <c r="J1380" t="n">
+        <v>78436.00833333333</v>
+      </c>
+      <c r="K1380" t="n">
+        <v>0.2832394369040325</v>
+      </c>
+      <c r="L1380" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1381" t="n">
+        <v>9326.625</v>
+      </c>
+      <c r="C1381" t="n">
+        <v>22068.48333333333</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>32003.29166666667</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>1019.525</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>8044.25</v>
+      </c>
+      <c r="G1381" t="n">
+        <v>5452.75</v>
+      </c>
+      <c r="H1381" t="n">
+        <v>138.7458333333333</v>
+      </c>
+      <c r="I1381" t="n">
+        <v>940.0791666666665</v>
+      </c>
+      <c r="J1381" t="n">
+        <v>78993.75</v>
+      </c>
+      <c r="K1381" t="n">
+        <v>0.1708616187989556</v>
+      </c>
+      <c r="L1381" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1382" t="n">
+        <v>9350.508333333333</v>
+      </c>
+      <c r="C1382" t="n">
+        <v>23094.38333333333</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>34255.06666666667</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>1090.3625</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>4821.325</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>2499.5875</v>
+      </c>
+      <c r="H1382" t="n">
+        <v>161.425</v>
+      </c>
+      <c r="I1382" t="n">
+        <v>905.7958333333332</v>
+      </c>
+      <c r="J1382" t="n">
+        <v>76178.45416666666</v>
+      </c>
+      <c r="K1382" t="n">
+        <v>0.09610214042914257</v>
+      </c>
+      <c r="L1382" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1383" t="n">
+        <v>9357.829166666666</v>
+      </c>
+      <c r="C1383" t="n">
+        <v>20276.12916666667</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>30071.9375</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>697.9499999999999</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>11365.26666666667</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>2738.866666666666</v>
+      </c>
+      <c r="H1383" t="n">
+        <v>63.04583333333333</v>
+      </c>
+      <c r="I1383" t="n">
+        <v>613.3458333333334</v>
+      </c>
+      <c r="J1383" t="n">
+        <v>75184.37083333333</v>
+      </c>
+      <c r="K1383" t="n">
+        <v>0.1875939530650458</v>
+      </c>
+      <c r="L1383" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1384" t="n">
+        <v>9330.995833333332</v>
+      </c>
+      <c r="C1384" t="n">
+        <v>15094.87916666667</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>22873.30416666667</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>649.3166666666666</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>20069.075</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>2583.129166666667</v>
+      </c>
+      <c r="H1384" t="n">
+        <v>84.39999999999999</v>
+      </c>
+      <c r="I1384" t="n">
+        <v>546.3208333333333</v>
+      </c>
+      <c r="J1384" t="n">
+        <v>71231.42083333334</v>
+      </c>
+      <c r="K1384" t="n">
+        <v>0.318008596510634</v>
+      </c>
+      <c r="L1384" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1385" t="n">
+        <v>8337.695833333333</v>
+      </c>
+      <c r="C1385" t="n">
+        <v>14349.89583333333</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>20270.4125</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>613.0625</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>14337.27083333333</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>6882.887500000001</v>
+      </c>
+      <c r="H1385" t="n">
+        <v>134.7375</v>
+      </c>
+      <c r="I1385" t="n">
+        <v>477.3083333333334</v>
+      </c>
+      <c r="J1385" t="n">
+        <v>65403.27083333334</v>
+      </c>
+      <c r="K1385" t="n">
+        <v>0.3244510261177687</v>
+      </c>
+      <c r="L1385" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1386" t="n">
+        <v>8335.391666666666</v>
+      </c>
+      <c r="C1386" t="n">
+        <v>12690.15416666667</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>17582.39583333333</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>591.9458333333333</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>19225.8375</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>6744.833333333333</v>
+      </c>
+      <c r="H1386" t="n">
+        <v>83.40833333333333</v>
+      </c>
+      <c r="I1386" t="n">
+        <v>484.2291666666667</v>
+      </c>
+      <c r="J1386" t="n">
+        <v>65738.19583333333</v>
+      </c>
+      <c r="K1386" t="n">
+        <v>0.3950621172990055</v>
+      </c>
+      <c r="L1386" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1387" t="n">
+        <v>8326.991666666667</v>
+      </c>
+      <c r="C1387" t="n">
+        <v>17099.25833333333</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>27660.28333333334</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>711.4083333333334</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>7427.333333333333</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>6555.170833333333</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>188.225</v>
+      </c>
+      <c r="I1387" t="n">
+        <v>567.6541666666667</v>
+      </c>
+      <c r="J1387" t="n">
+        <v>68536.325</v>
+      </c>
+      <c r="K1387" t="n">
+        <v>0.2040159603927796</v>
+      </c>
+      <c r="L1387" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1388" t="n">
+        <v>8323.041666666666</v>
+      </c>
+      <c r="C1388" t="n">
+        <v>17196.84583333333</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>25947.77916666666</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>676.8208333333333</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>8384.095833333333</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>6198.520833333333</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>93.10000000000001</v>
+      </c>
+      <c r="I1388" t="n">
+        <v>608.7791666666667</v>
+      </c>
+      <c r="J1388" t="n">
+        <v>67428.98333333334</v>
+      </c>
+      <c r="K1388" t="n">
+        <v>0.2162662989382162</v>
+      </c>
+      <c r="L1388" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1389" t="n">
+        <v>8316.345833333333</v>
+      </c>
+      <c r="C1389" t="n">
+        <v>17318.02916666666</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>28447.62083333333</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>671.3208333333333</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>5884.3125</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>5871.095833333333</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="I1389" t="n">
+        <v>608.8541666666666</v>
+      </c>
+      <c r="J1389" t="n">
+        <v>67218.27916666667</v>
+      </c>
+      <c r="K1389" t="n">
+        <v>0.1748841011562641</v>
+      </c>
+      <c r="L1389" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1390" t="n">
+        <v>8318.829166666666</v>
+      </c>
+      <c r="C1390" t="n">
+        <v>17163.54166666667</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>28938.19583333333</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>705.3958333333334</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>6436.899999999999</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>6034.620833333333</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>81.36666666666667</v>
+      </c>
+      <c r="I1390" t="n">
+        <v>609</v>
+      </c>
+      <c r="J1390" t="n">
+        <v>68287.84999999999</v>
+      </c>
+      <c r="K1390" t="n">
+        <v>0.182631622365228</v>
+      </c>
+      <c r="L1390" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1391" t="n">
+        <v>8310.625</v>
+      </c>
+      <c r="C1391" t="n">
+        <v>14244.06666666667</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>24559.0875</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>596.2541666666666</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>16107.15416666667</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>6029.5125</v>
+      </c>
+      <c r="H1391" t="n">
+        <v>97.09999999999998</v>
+      </c>
+      <c r="I1391" t="n">
+        <v>572.4</v>
+      </c>
+      <c r="J1391" t="n">
+        <v>70516.2</v>
+      </c>
+      <c r="K1391" t="n">
+        <v>0.3139231363384111</v>
+      </c>
+      <c r="L1391" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1392" t="n">
+        <v>8310.279166666667</v>
+      </c>
+      <c r="C1392" t="n">
+        <v>13594.44583333333</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>23131.70416666666</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>572.3583333333332</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>13786.75416666667</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>5583.704166666666</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>77.65416666666665</v>
+      </c>
+      <c r="I1392" t="n">
+        <v>561.2208333333333</v>
+      </c>
+      <c r="J1392" t="n">
+        <v>65618.12083333333</v>
+      </c>
+      <c r="K1392" t="n">
+        <v>0.2951998333285603</v>
+      </c>
+      <c r="L1392" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1393" t="n">
+        <v>8316.745833333332</v>
+      </c>
+      <c r="C1393" t="n">
+        <v>15831.07083333333</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>26018.39583333333</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>599.5791666666668</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>6620.870833333333</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>5300.366666666667</v>
+      </c>
+      <c r="H1393" t="n">
+        <v>99.40833333333335</v>
+      </c>
+      <c r="I1393" t="n">
+        <v>562.0875</v>
+      </c>
+      <c r="J1393" t="n">
+        <v>63348.525</v>
+      </c>
+      <c r="K1393" t="n">
+        <v>0.1881849261683678</v>
+      </c>
+      <c r="L1393" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1394" t="n">
+        <v>8316.695833333333</v>
+      </c>
+      <c r="C1394" t="n">
+        <v>16761.06666666667</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>29758.98333333333</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>587.9791666666666</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>10117.01666666667</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>4227.795833333334</v>
+      </c>
+      <c r="H1394" t="n">
+        <v>120.425</v>
+      </c>
+      <c r="I1394" t="n">
+        <v>582.9166666666666</v>
+      </c>
+      <c r="J1394" t="n">
+        <v>70472.87916666667</v>
+      </c>
+      <c r="K1394" t="n">
+        <v>0.2035508222400686</v>
+      </c>
+      <c r="L1394" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
@@ -2095,25 +2095,25 @@
         <v>46296</v>
       </c>
       <c r="B47" t="n">
-        <v>26548.88429487179</v>
+        <v>26724.90709876543</v>
       </c>
       <c r="C47" t="n">
-        <v>17474.57243589743</v>
+        <v>17482.30077160494</v>
       </c>
       <c r="D47" t="n">
-        <v>11300.04711538461</v>
+        <v>11191.56203703704</v>
       </c>
       <c r="E47" t="n">
-        <v>9198.352083333333</v>
+        <v>9165.774074074074</v>
       </c>
       <c r="F47" t="n">
-        <v>5482.638942307693</v>
+        <v>5411.45339506173</v>
       </c>
       <c r="G47" t="n">
-        <v>804.1891025641027</v>
+        <v>795.3560185185187</v>
       </c>
       <c r="H47" t="n">
-        <v>130.3455128205128</v>
+        <v>130.6240740740741</v>
       </c>
     </row>
   </sheetData>
@@ -2128,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1394"/>
+  <dimension ref="A1:L1395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -55130,6 +55130,44 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1395">
+      <c r="A1395" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1395" t="n">
+        <v>8318.745833333334</v>
+      </c>
+      <c r="C1395" t="n">
+        <v>17683.2375</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>31301.5</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>565.6958333333333</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>8370.949999999999</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>3560.629166666667</v>
+      </c>
+      <c r="H1395" t="n">
+        <v>113.8666666666667</v>
+      </c>
+      <c r="I1395" t="n">
+        <v>598.6999999999999</v>
+      </c>
+      <c r="J1395" t="n">
+        <v>70513.325</v>
+      </c>
+      <c r="K1395" t="n">
+        <v>0.1692102757410272</v>
+      </c>
+      <c r="L1395" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
@@ -2095,25 +2095,25 @@
         <v>46296</v>
       </c>
       <c r="B47" t="n">
-        <v>26724.90709876543</v>
+        <v>26763.82276785714</v>
       </c>
       <c r="C47" t="n">
-        <v>17482.30077160494</v>
+        <v>17423.23794642857</v>
       </c>
       <c r="D47" t="n">
-        <v>11191.56203703704</v>
+        <v>11276.69806547619</v>
       </c>
       <c r="E47" t="n">
-        <v>9165.774074074074</v>
+        <v>9135.246279761905</v>
       </c>
       <c r="F47" t="n">
-        <v>5411.45339506173</v>
+        <v>5399.343750000001</v>
       </c>
       <c r="G47" t="n">
-        <v>795.3560185185187</v>
+        <v>785.9627976190477</v>
       </c>
       <c r="H47" t="n">
-        <v>130.6240740740741</v>
+        <v>129.5943452380952</v>
       </c>
     </row>
   </sheetData>
@@ -2128,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1395"/>
+  <dimension ref="A1:L1396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -55168,6 +55168,44 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1396">
+      <c r="A1396" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1396" t="n">
+        <v>8310.995833333334</v>
+      </c>
+      <c r="C1396" t="n">
+        <v>15828.54166666667</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>27814.54583333333</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>532.3458333333333</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>13575.37083333333</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>5072.383333333334</v>
+      </c>
+      <c r="H1396" t="n">
+        <v>77.79166666666664</v>
+      </c>
+      <c r="I1396" t="n">
+        <v>571.9666666666667</v>
+      </c>
+      <c r="J1396" t="n">
+        <v>71783.94166666667</v>
+      </c>
+      <c r="K1396" t="n">
+        <v>0.2597761244883808</v>
+      </c>
+      <c r="L1396" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/miso_fuel_mix_daily.xlsx
@@ -2095,25 +2095,25 @@
         <v>46296</v>
       </c>
       <c r="B47" t="n">
-        <v>26763.82276785714</v>
+        <v>26843.00646551724</v>
       </c>
       <c r="C47" t="n">
-        <v>17423.23794642857</v>
+        <v>17406.99252873563</v>
       </c>
       <c r="D47" t="n">
-        <v>11276.69806547619</v>
+        <v>11211.52801724138</v>
       </c>
       <c r="E47" t="n">
-        <v>9135.246279761905</v>
+        <v>9106.841810344828</v>
       </c>
       <c r="F47" t="n">
-        <v>5399.343750000001</v>
+        <v>5381.802873563219</v>
       </c>
       <c r="G47" t="n">
-        <v>785.9627976190477</v>
+        <v>776.4955459770115</v>
       </c>
       <c r="H47" t="n">
-        <v>129.5943452380952</v>
+        <v>128.8790229885058</v>
       </c>
     </row>
   </sheetData>
@@ -2128,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1396"/>
+  <dimension ref="A1:L1397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -55206,6 +55206,44 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1397">
+      <c r="A1397" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1397" t="n">
+        <v>8311.516666666666</v>
+      </c>
+      <c r="C1397" t="n">
+        <v>16952.12083333333</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>29060.15000000001</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>511.4125</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>9386.766666666666</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>4890.658333333333</v>
+      </c>
+      <c r="H1397" t="n">
+        <v>84.85000000000001</v>
+      </c>
+      <c r="I1397" t="n">
+        <v>590.3166666666666</v>
+      </c>
+      <c r="J1397" t="n">
+        <v>69787.79166666667</v>
+      </c>
+      <c r="K1397" t="n">
+        <v>0.204583418661454</v>
+      </c>
+      <c r="L1397" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
